--- a/real_estate_prospects.xlsx
+++ b/real_estate_prospects.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2029"/>
+  <dimension ref="A1:I2032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71455,6 +71455,111 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2030">
+      <c r="A2030" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B2030" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2030" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2030" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2030" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B2031" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2031" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2031" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2031" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B2032" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2032" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2032" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2032" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
